--- a/internal_doc/05.测试设计/sdv/基本操作/基本操作_SDV表格.xlsx
+++ b/internal_doc/05.测试设计/sdv/基本操作/基本操作_SDV表格.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="5940"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="5940" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="正常" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="177">
   <si>
     <t>记录类型</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -181,305 +181,297 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>大数据量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通记录+lob</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>300MB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16MB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不并发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100insert+100query+1update+1delete</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>线程数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>百条</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10条</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>insert方式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>连接coord数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重要测试点：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>关注点：（关注贴近用户的场景，只做覆盖）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>正常/异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>写lob的同时，删除lob</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新同一条记录的同时，删除记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1 查询时关注数据一致性，即主备节点的数据一致</t>
+  </si>
+  <si>
+    <t>注释：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>insert+query+update+upsert+findAndModify+cursor+delete</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>upsert+cursor+update+findAndModify+insert+query+delete</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query+insert+delete+upsert+findAndModify+cursor+update+query</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>混合使用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">2 lob与记录混合使用时，lob数量与记录数量是一对一的。 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>300MB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>author:余婷 时间：20150618</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大数据量（磁盘的80%）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bulkInsert</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动创建_id索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>否</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进程正常退出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进程异常退出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络长断</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>机器正常关机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>机器异常关机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据主节点故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>整个数据组故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据1个备节点故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>整个数据库故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>与sdb的网络</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3 离线索引因为开发未完成，所以未纳入sdv</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>磁盘满盘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据备节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>协调节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>√</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络闪断</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络长断</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>√与sdb的网络</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>整个数据组</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>整个数据库</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>√与数据主节点的网络</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>与数据主节点的网络</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无法写入数据，网络恢复后可以正常操作，副本之间数据一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以写入数据，用户不感知到网络闪断</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已写入的数据不会丢，重启后可以正常操作，副本之间数据一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>写入磁盘的数据不会丢，在内存的数据会丢，即会有一部分的数据丢失，重启后索引重建，可以正常操作，副本之间数据一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>与某个备节点的闪断</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>与大多数节点的闪断</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪断时，主节点不会降备，可以正常操作；网络恢复后，备节点作数据同步，副本间数据一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>与某个备节点的长断</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>与大多数节点的长断</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络闪断7s</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>√与某个备节点的闪断</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>√与大多数节点的闪断</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>√与某个备节点的长断</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>√与大多数节点的长断</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>场景</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>大数据量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>普通记录+lob</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>300MB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>16MB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不并发</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>100insert+100query+1update+1delete</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>线程数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>百条</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10条</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>insert方式</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>索引</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>连接coord数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>重要测试点：</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>关注点：（关注贴近用户的场景，只做覆盖）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>正常/异常</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>正常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>异常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>写lob的同时，删除lob</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>更新同一条记录的同时，删除记录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1 查询时关注数据一致性，即主备节点的数据一致</t>
-  </si>
-  <si>
-    <t>注释：</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>insert+query+update+upsert+findAndModify+cursor+delete</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>upsert+cursor+update+findAndModify+insert+query+delete</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>query+insert+delete+upsert+findAndModify+cursor+update+query</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>混合使用</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">2 lob与记录混合使用时，lob数量与记录数量是一对一的。 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>300MB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>author:余婷 时间：20150618</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>大数据量（磁盘的80%）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bulkInsert</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自动创建_id索引</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>否</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进程正常退出</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进程异常退出</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网络长断</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>机器正常关机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>机器异常关机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据主节点故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>整个数据组故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>异常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据1个备节点故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>整个数据库故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>与sdb的网络</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3 离线索引因为开发未完成，所以未纳入sdv</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>磁盘满盘</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据备节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>协调节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>√</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网络闪断</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网络长断</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>√与sdb的网络</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>整个数据组</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>整个数据库</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>√与数据主节点的网络</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>与数据主节点的网络</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>无法写入数据，网络恢复后可以正常操作，副本之间数据一致</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>可以写入数据，用户不感知到网络闪断</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>已写入的数据不会丢，重启后可以正常操作，副本之间数据一致</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>写入磁盘的数据不会丢，在内存的数据会丢，即会有一部分的数据丢失，重启后索引重建，可以正常操作，副本之间数据一致</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>与某个备节点的闪断</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>与大多数节点的闪断</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>闪断时，主节点不会降备，可以正常操作；网络恢复后，备节点作数据同步，副本间数据一致</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>与某个备节点的长断</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>与大多数节点的长断</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网络闪断7s</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>√与某个备节点的闪断</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>√与大多数节点的闪断</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>√与某个备节点的长断</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>√与大多数节点的长断</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>场景</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>正常/异常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>序号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>预期结果</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -553,6 +545,143 @@
   </si>
   <si>
     <t>网络闪断30s</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001.001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001.002</t>
+  </si>
+  <si>
+    <t>001.003</t>
+  </si>
+  <si>
+    <t>001.004</t>
+  </si>
+  <si>
+    <t>001.005</t>
+  </si>
+  <si>
+    <t>001.006</t>
+  </si>
+  <si>
+    <t>001.007</t>
+  </si>
+  <si>
+    <t>001.008</t>
+  </si>
+  <si>
+    <t>001.009</t>
+  </si>
+  <si>
+    <t>001.010</t>
+  </si>
+  <si>
+    <t>002.001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002.002</t>
+  </si>
+  <si>
+    <t>002.003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002.004</t>
+  </si>
+  <si>
+    <t>002.005</t>
+  </si>
+  <si>
+    <t>002.006</t>
+  </si>
+  <si>
+    <t>002.007</t>
+  </si>
+  <si>
+    <t>002.008</t>
+  </si>
+  <si>
+    <t>002.009</t>
+  </si>
+  <si>
+    <t>002.010</t>
+  </si>
+  <si>
+    <t>002.011</t>
+  </si>
+  <si>
+    <t>002.012</t>
+  </si>
+  <si>
+    <t>002.013</t>
+  </si>
+  <si>
+    <t>002.014</t>
+  </si>
+  <si>
+    <t>002.015</t>
+  </si>
+  <si>
+    <t>002.016</t>
+  </si>
+  <si>
+    <t>002.017</t>
+  </si>
+  <si>
+    <t>002.018</t>
+  </si>
+  <si>
+    <t>002.019</t>
+  </si>
+  <si>
+    <t>002.020</t>
+  </si>
+  <si>
+    <t>002.021</t>
+  </si>
+  <si>
+    <t>002.022</t>
+  </si>
+  <si>
+    <t>002.023</t>
+  </si>
+  <si>
+    <t>002.024</t>
+  </si>
+  <si>
+    <t>002.025</t>
+  </si>
+  <si>
+    <t>002.026</t>
+  </si>
+  <si>
+    <t>002.027</t>
+  </si>
+  <si>
+    <t>002.028</t>
+  </si>
+  <si>
+    <t>002.029</t>
+  </si>
+  <si>
+    <t>002.030</t>
+  </si>
+  <si>
+    <t>002.031</t>
+  </si>
+  <si>
+    <t>002.032</t>
+  </si>
+  <si>
+    <t>编号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -728,7 +857,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -832,6 +961,10 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1197,7 +1330,7 @@
   <dimension ref="A2:Q85"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="4.875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="10.75" style="2" customWidth="1"/>
     <col min="2" max="2" width="8" style="2" customWidth="1"/>
     <col min="3" max="3" width="6" style="2" customWidth="1"/>
     <col min="4" max="4" width="10.375" style="2" customWidth="1"/>
@@ -1218,7 +1351,7 @@
   <sheetData>
     <row r="2" spans="1:17">
       <c r="D2" s="28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E2" s="29"/>
       <c r="F2" s="29"/>
@@ -1253,10 +1386,10 @@
         <v>26</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M3"/>
     </row>
@@ -1275,13 +1408,13 @@
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L4" s="4">
         <v>1</v>
@@ -1293,7 +1426,7 @@
         <v>28</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>8</v>
@@ -1309,7 +1442,7 @@
         <v>27</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L5" s="4">
         <v>3</v>
@@ -1318,7 +1451,7 @@
     </row>
     <row r="6" spans="1:17">
       <c r="D6" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E6" s="15"/>
       <c r="F6" s="15"/>
@@ -1332,7 +1465,7 @@
     </row>
     <row r="8" spans="1:17">
       <c r="D8" s="28" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E8" s="29"/>
       <c r="F8" s="29"/>
@@ -1340,7 +1473,7 @@
       <c r="H8" s="29"/>
       <c r="I8" s="30"/>
       <c r="K8" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -1357,14 +1490,14 @@
         <v>9</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>25</v>
       </c>
       <c r="J9"/>
       <c r="K9" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -1384,11 +1517,11 @@
         <v>29</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J10"/>
       <c r="K10" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -1396,7 +1529,7 @@
         <v>21</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>11</v>
@@ -1412,13 +1545,13 @@
       </c>
       <c r="J11"/>
       <c r="K11" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:17">
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
@@ -1426,7 +1559,7 @@
       <c r="I12" s="4"/>
       <c r="J12"/>
       <c r="K12" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -1441,7 +1574,7 @@
     </row>
     <row r="14" spans="1:17">
       <c r="A14" s="31" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B14" s="31"/>
       <c r="C14" s="31"/>
@@ -1461,10 +1594,10 @@
     </row>
     <row r="15" spans="1:17" ht="54">
       <c r="A15" s="14" t="s">
-        <v>41</v>
+        <v>176</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>19</v>
@@ -1476,10 +1609,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G15" s="8" t="s">
         <v>51</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>52</v>
       </c>
       <c r="H15" s="8" t="s">
         <v>9</v>
@@ -1497,28 +1630,28 @@
         <v>22</v>
       </c>
       <c r="M15" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N15" s="14" t="s">
         <v>26</v>
       </c>
       <c r="O15" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P15" s="14" t="s">
         <v>33</v>
       </c>
       <c r="Q15" s="1"/>
     </row>
-    <row r="16" spans="1:17">
-      <c r="A16" s="6">
-        <v>1</v>
+    <row r="16" spans="1:17" ht="27">
+      <c r="A16" s="43" t="s">
+        <v>133</v>
       </c>
       <c r="B16" s="32" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16" s="32" t="s">
         <v>4</v>
@@ -1550,16 +1683,16 @@
         <v>27</v>
       </c>
       <c r="O16" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q16" s="1"/>
     </row>
     <row r="17" spans="1:17">
-      <c r="A17" s="6">
-        <v>2</v>
+      <c r="A17" s="43" t="s">
+        <v>134</v>
       </c>
       <c r="B17" s="32"/>
       <c r="C17" s="32"/>
@@ -1589,16 +1722,16 @@
         <v>27</v>
       </c>
       <c r="O17" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P17" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q17" s="1"/>
     </row>
     <row r="18" spans="1:17">
-      <c r="A18" s="6">
-        <v>3</v>
+      <c r="A18" s="43" t="s">
+        <v>135</v>
       </c>
       <c r="B18" s="32"/>
       <c r="C18" s="32"/>
@@ -1624,7 +1757,7 @@
         <v>27</v>
       </c>
       <c r="O18" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P18" s="6" t="s">
         <v>34</v>
@@ -1632,8 +1765,8 @@
       <c r="Q18" s="1"/>
     </row>
     <row r="19" spans="1:17">
-      <c r="A19" s="6">
-        <v>4</v>
+      <c r="A19" s="43" t="s">
+        <v>136</v>
       </c>
       <c r="B19" s="32"/>
       <c r="C19" s="32"/>
@@ -1667,16 +1800,16 @@
         <v>27</v>
       </c>
       <c r="O19" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P19" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Q19" s="1"/>
     </row>
     <row r="20" spans="1:17" ht="27">
-      <c r="A20" s="6">
-        <v>5</v>
+      <c r="A20" s="43" t="s">
+        <v>137</v>
       </c>
       <c r="B20" s="32"/>
       <c r="C20" s="32"/>
@@ -1706,23 +1839,23 @@
         <v>27</v>
       </c>
       <c r="O20" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q20" s="1"/>
     </row>
     <row r="21" spans="1:17">
-      <c r="A21" s="6">
-        <v>6</v>
+      <c r="A21" s="43" t="s">
+        <v>138</v>
       </c>
       <c r="B21" s="32"/>
       <c r="C21" s="32"/>
       <c r="D21" s="32"/>
       <c r="E21" s="38"/>
       <c r="F21" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G21" s="11" t="s">
         <v>8</v>
@@ -1743,16 +1876,16 @@
       </c>
       <c r="N21" s="7"/>
       <c r="O21" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P21" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q21" s="1"/>
     </row>
     <row r="22" spans="1:17">
-      <c r="A22" s="6">
-        <v>7</v>
+      <c r="A22" s="43" t="s">
+        <v>139</v>
       </c>
       <c r="B22" s="32"/>
       <c r="C22" s="32"/>
@@ -1769,7 +1902,7 @@
         <v>21</v>
       </c>
       <c r="L22" s="13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M22" s="12" t="s">
         <v>32</v>
@@ -1778,7 +1911,7 @@
         <v>27</v>
       </c>
       <c r="O22" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>40</v>
@@ -1786,16 +1919,16 @@
       <c r="Q22" s="1"/>
     </row>
     <row r="23" spans="1:17" ht="27">
-      <c r="A23" s="6">
-        <v>8</v>
+      <c r="A23" s="43" t="s">
+        <v>140</v>
       </c>
       <c r="B23" s="32"/>
       <c r="C23" s="32"/>
       <c r="D23" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E23" s="7" t="s">
         <v>42</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>43</v>
       </c>
       <c r="F23" s="11" t="s">
         <v>39</v>
@@ -1816,7 +1949,7 @@
         <v>15</v>
       </c>
       <c r="L23" s="13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M23" s="12" t="s">
         <v>32</v>
@@ -1825,26 +1958,26 @@
         <v>27</v>
       </c>
       <c r="O23" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P23" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="Q23" s="1"/>
     </row>
     <row r="24" spans="1:17" ht="27">
-      <c r="A24" s="6">
-        <v>9</v>
+      <c r="A24" s="43" t="s">
+        <v>141</v>
       </c>
       <c r="B24" s="32"/>
       <c r="C24" s="32" t="s">
         <v>20</v>
       </c>
       <c r="D24" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E24" s="7" t="s">
         <v>42</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>43</v>
       </c>
       <c r="F24" s="11" t="s">
         <v>39</v>
@@ -1865,7 +1998,7 @@
         <v>15</v>
       </c>
       <c r="L24" s="13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M24" s="7">
         <v>3</v>
@@ -1874,21 +2007,21 @@
         <v>27</v>
       </c>
       <c r="O24" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="Q24" s="1"/>
     </row>
     <row r="25" spans="1:17">
-      <c r="A25" s="6">
-        <v>10</v>
+      <c r="A25" s="43" t="s">
+        <v>142</v>
       </c>
       <c r="B25" s="32"/>
       <c r="C25" s="32"/>
       <c r="D25" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E25" s="11" t="s">
         <v>2</v>
@@ -1917,19 +2050,19 @@
         <v>6</v>
       </c>
       <c r="O25" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P25" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q25" s="1"/>
     </row>
     <row r="26" spans="1:17">
-      <c r="A26" s="6">
-        <v>1</v>
+      <c r="A26" s="43" t="s">
+        <v>143</v>
       </c>
       <c r="B26" s="33" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C26" s="34" t="s">
         <v>20</v>
@@ -1964,15 +2097,15 @@
         <v>27</v>
       </c>
       <c r="O26" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P26" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27" spans="1:17">
-      <c r="A27" s="6">
-        <v>2</v>
+      <c r="A27" s="43" t="s">
+        <v>144</v>
       </c>
       <c r="B27" s="33"/>
       <c r="C27" s="34"/>
@@ -1989,7 +2122,7 @@
         <v>15</v>
       </c>
       <c r="L27" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M27" s="7">
         <v>1</v>
@@ -1998,10 +2131,10 @@
         <v>27</v>
       </c>
       <c r="O27" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P27" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:17">
@@ -2237,70 +2370,70 @@
     <row r="2" spans="1:15">
       <c r="B2" s="4"/>
       <c r="C2" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>90</v>
-      </c>
       <c r="F2" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>95</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:15">
       <c r="B3" s="15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="B4" s="15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="B5" s="15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
@@ -2308,14 +2441,14 @@
     </row>
     <row r="6" spans="1:15">
       <c r="B6" s="34" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D6" s="34"/>
       <c r="E6" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
@@ -2323,25 +2456,25 @@
     <row r="7" spans="1:15">
       <c r="B7" s="34"/>
       <c r="C7" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D7" s="34"/>
       <c r="E7" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:15">
       <c r="B8" s="34" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D8" s="34"/>
       <c r="E8" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
@@ -2349,58 +2482,58 @@
     <row r="9" spans="1:15">
       <c r="B9" s="34"/>
       <c r="C9" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D9" s="34"/>
       <c r="E9" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
     </row>
     <row r="10" spans="1:15">
       <c r="B10" s="15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="B11" s="15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="31" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B14" s="31"/>
       <c r="C14" s="31"/>
@@ -2419,20 +2552,20 @@
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="25" t="s">
-        <v>115</v>
+        <v>175</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E15" s="39"/>
       <c r="F15" s="40" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G15" s="41"/>
       <c r="H15" s="41"/>
@@ -2445,21 +2578,21 @@
       <c r="O15" s="42"/>
     </row>
     <row r="16" spans="1:15">
-      <c r="A16" s="4">
-        <v>3</v>
+      <c r="A16" s="44" t="s">
+        <v>145</v>
       </c>
       <c r="B16" s="34" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C16" s="34" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="31" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G16" s="31"/>
       <c r="H16" s="31"/>
@@ -2472,13 +2605,13 @@
       <c r="O16" s="31"/>
     </row>
     <row r="17" spans="1:15">
-      <c r="A17" s="4">
-        <v>4</v>
+      <c r="A17" s="44" t="s">
+        <v>146</v>
       </c>
       <c r="B17" s="34"/>
       <c r="C17" s="34"/>
       <c r="D17" s="22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="31">
@@ -2495,17 +2628,17 @@
       <c r="O17" s="31"/>
     </row>
     <row r="18" spans="1:15">
-      <c r="A18" s="4">
-        <v>5</v>
+      <c r="A18" s="44" t="s">
+        <v>147</v>
       </c>
       <c r="B18" s="34"/>
       <c r="C18" s="34"/>
       <c r="D18" s="15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="31" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G18" s="31"/>
       <c r="H18" s="31"/>
@@ -2518,19 +2651,19 @@
       <c r="O18" s="31"/>
     </row>
     <row r="19" spans="1:15">
-      <c r="A19" s="4">
-        <v>6</v>
+      <c r="A19" s="44" t="s">
+        <v>148</v>
       </c>
       <c r="B19" s="34"/>
       <c r="C19" s="34"/>
       <c r="D19" s="34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F19" s="31" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G19" s="31"/>
       <c r="H19" s="31"/>
@@ -2543,17 +2676,17 @@
       <c r="O19" s="31"/>
     </row>
     <row r="20" spans="1:15">
-      <c r="A20" s="4">
-        <v>7</v>
+      <c r="A20" s="44" t="s">
+        <v>149</v>
       </c>
       <c r="B20" s="34"/>
       <c r="C20" s="34"/>
       <c r="D20" s="34"/>
       <c r="E20" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F20" s="31" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G20" s="31"/>
       <c r="H20" s="31"/>
@@ -2566,19 +2699,19 @@
       <c r="O20" s="31"/>
     </row>
     <row r="21" spans="1:15">
-      <c r="A21" s="4">
-        <v>8</v>
+      <c r="A21" s="44" t="s">
+        <v>150</v>
       </c>
       <c r="B21" s="34"/>
       <c r="C21" s="34"/>
       <c r="D21" s="34" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F21" s="31" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G21" s="31"/>
       <c r="H21" s="31"/>
@@ -2591,17 +2724,17 @@
       <c r="O21" s="31"/>
     </row>
     <row r="22" spans="1:15">
-      <c r="A22" s="4">
-        <v>9</v>
+      <c r="A22" s="44" t="s">
+        <v>151</v>
       </c>
       <c r="B22" s="34"/>
       <c r="C22" s="34"/>
       <c r="D22" s="34"/>
       <c r="E22" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F22" s="31" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G22" s="31"/>
       <c r="H22" s="31"/>
@@ -2614,13 +2747,13 @@
       <c r="O22" s="31"/>
     </row>
     <row r="23" spans="1:15">
-      <c r="A23" s="4">
-        <v>10</v>
+      <c r="A23" s="44" t="s">
+        <v>152</v>
       </c>
       <c r="B23" s="34"/>
       <c r="C23" s="34"/>
       <c r="D23" s="15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E23" s="4"/>
       <c r="F23" s="31">
@@ -2637,13 +2770,13 @@
       <c r="O23" s="31"/>
     </row>
     <row r="24" spans="1:15">
-      <c r="A24" s="4">
-        <v>11</v>
+      <c r="A24" s="44" t="s">
+        <v>153</v>
       </c>
       <c r="B24" s="34"/>
       <c r="C24" s="34"/>
       <c r="D24" s="22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E24" s="4"/>
       <c r="F24" s="31">
@@ -2660,19 +2793,19 @@
       <c r="O24" s="31"/>
     </row>
     <row r="25" spans="1:15">
-      <c r="A25" s="4">
-        <v>12</v>
+      <c r="A25" s="44" t="s">
+        <v>154</v>
       </c>
       <c r="B25" s="34"/>
       <c r="C25" s="34" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D25" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E25" s="4"/>
       <c r="F25" s="31" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G25" s="31"/>
       <c r="H25" s="31"/>
@@ -2685,17 +2818,17 @@
       <c r="O25" s="31"/>
     </row>
     <row r="26" spans="1:15">
-      <c r="A26" s="4">
-        <v>13</v>
+      <c r="A26" s="44" t="s">
+        <v>155</v>
       </c>
       <c r="B26" s="34"/>
       <c r="C26" s="34"/>
       <c r="D26" s="22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E26" s="4"/>
       <c r="F26" s="31" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G26" s="31"/>
       <c r="H26" s="31"/>
@@ -2708,17 +2841,17 @@
       <c r="O26" s="31"/>
     </row>
     <row r="27" spans="1:15">
-      <c r="A27" s="4">
-        <v>14</v>
+      <c r="A27" s="44" t="s">
+        <v>156</v>
       </c>
       <c r="B27" s="34"/>
       <c r="C27" s="34"/>
       <c r="D27" s="15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E27" s="4"/>
       <c r="F27" s="31" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G27" s="31"/>
       <c r="H27" s="31"/>
@@ -2731,13 +2864,13 @@
       <c r="O27" s="31"/>
     </row>
     <row r="28" spans="1:15">
-      <c r="A28" s="4">
-        <v>15</v>
+      <c r="A28" s="44" t="s">
+        <v>157</v>
       </c>
       <c r="B28" s="34"/>
       <c r="C28" s="34"/>
       <c r="D28" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E28" s="4"/>
       <c r="F28" s="31">
@@ -2754,17 +2887,17 @@
       <c r="O28" s="31"/>
     </row>
     <row r="29" spans="1:15">
-      <c r="A29" s="4">
-        <v>16</v>
+      <c r="A29" s="44" t="s">
+        <v>158</v>
       </c>
       <c r="B29" s="34"/>
       <c r="C29" s="34"/>
       <c r="D29" s="22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E29" s="4"/>
       <c r="F29" s="31" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G29" s="31"/>
       <c r="H29" s="31"/>
@@ -2777,19 +2910,19 @@
       <c r="O29" s="31"/>
     </row>
     <row r="30" spans="1:15">
-      <c r="A30" s="4">
-        <v>17</v>
+      <c r="A30" s="44" t="s">
+        <v>159</v>
       </c>
       <c r="B30" s="34"/>
       <c r="C30" s="34" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E30" s="4"/>
       <c r="F30" s="31" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G30" s="31"/>
       <c r="H30" s="31"/>
@@ -2802,17 +2935,17 @@
       <c r="O30" s="31"/>
     </row>
     <row r="31" spans="1:15">
-      <c r="A31" s="4">
-        <v>18</v>
+      <c r="A31" s="44" t="s">
+        <v>160</v>
       </c>
       <c r="B31" s="34"/>
       <c r="C31" s="34"/>
       <c r="D31" s="15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E31" s="4"/>
       <c r="F31" s="31" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G31" s="31"/>
       <c r="H31" s="31"/>
@@ -2825,19 +2958,19 @@
       <c r="O31" s="31"/>
     </row>
     <row r="32" spans="1:15">
-      <c r="A32" s="4">
-        <v>19</v>
+      <c r="A32" s="44" t="s">
+        <v>161</v>
       </c>
       <c r="B32" s="34"/>
       <c r="C32" s="34"/>
       <c r="D32" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F32" s="31" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G32" s="31"/>
       <c r="H32" s="31"/>
@@ -2850,17 +2983,17 @@
       <c r="O32" s="31"/>
     </row>
     <row r="33" spans="1:15">
-      <c r="A33" s="4">
-        <v>20</v>
+      <c r="A33" s="44" t="s">
+        <v>162</v>
       </c>
       <c r="B33" s="34"/>
       <c r="C33" s="34"/>
       <c r="D33" s="34"/>
       <c r="E33" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F33" s="31" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G33" s="31"/>
       <c r="H33" s="31"/>
@@ -2873,19 +3006,19 @@
       <c r="O33" s="31"/>
     </row>
     <row r="34" spans="1:15">
-      <c r="A34" s="4">
-        <v>21</v>
+      <c r="A34" s="44" t="s">
+        <v>163</v>
       </c>
       <c r="B34" s="34"/>
       <c r="C34" s="34"/>
       <c r="D34" s="34" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F34" s="31" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G34" s="31"/>
       <c r="H34" s="31"/>
@@ -2898,17 +3031,17 @@
       <c r="O34" s="31"/>
     </row>
     <row r="35" spans="1:15">
-      <c r="A35" s="4">
-        <v>22</v>
+      <c r="A35" s="44" t="s">
+        <v>164</v>
       </c>
       <c r="B35" s="34"/>
       <c r="C35" s="34"/>
       <c r="D35" s="34"/>
       <c r="E35" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F35" s="31" t="s">
         <v>98</v>
-      </c>
-      <c r="F35" s="31" t="s">
-        <v>99</v>
       </c>
       <c r="G35" s="31"/>
       <c r="H35" s="31"/>
@@ -2921,17 +3054,17 @@
       <c r="O35" s="31"/>
     </row>
     <row r="36" spans="1:15">
-      <c r="A36" s="4">
-        <v>23</v>
+      <c r="A36" s="44" t="s">
+        <v>165</v>
       </c>
       <c r="B36" s="34"/>
       <c r="C36" s="34"/>
       <c r="D36" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E36" s="4"/>
       <c r="F36" s="31" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G36" s="31"/>
       <c r="H36" s="31"/>
@@ -2944,17 +3077,17 @@
       <c r="O36" s="31"/>
     </row>
     <row r="37" spans="1:15">
-      <c r="A37" s="4">
-        <v>24</v>
+      <c r="A37" s="44" t="s">
+        <v>166</v>
       </c>
       <c r="B37" s="34"/>
       <c r="C37" s="34"/>
       <c r="D37" s="22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E37" s="4"/>
       <c r="F37" s="31" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G37" s="31"/>
       <c r="H37" s="31"/>
@@ -2967,15 +3100,15 @@
       <c r="O37" s="31"/>
     </row>
     <row r="38" spans="1:15">
-      <c r="A38" s="4">
-        <v>25</v>
+      <c r="A38" s="44" t="s">
+        <v>167</v>
       </c>
       <c r="B38" s="34"/>
       <c r="C38" s="34" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D38" s="24" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E38" s="4"/>
       <c r="F38" s="31">
@@ -2992,13 +3125,13 @@
       <c r="O38" s="31"/>
     </row>
     <row r="39" spans="1:15">
-      <c r="A39" s="4">
-        <v>26</v>
+      <c r="A39" s="44" t="s">
+        <v>168</v>
       </c>
       <c r="B39" s="34"/>
       <c r="C39" s="34"/>
       <c r="D39" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E39" s="4"/>
       <c r="F39" s="31">
@@ -3015,13 +3148,13 @@
       <c r="O39" s="31"/>
     </row>
     <row r="40" spans="1:15">
-      <c r="A40" s="4">
-        <v>27</v>
+      <c r="A40" s="44" t="s">
+        <v>169</v>
       </c>
       <c r="B40" s="34"/>
       <c r="C40" s="34"/>
       <c r="D40" s="24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E40" s="4"/>
       <c r="F40" s="31">
@@ -3038,13 +3171,13 @@
       <c r="O40" s="31"/>
     </row>
     <row r="41" spans="1:15">
-      <c r="A41" s="4">
-        <v>28</v>
+      <c r="A41" s="44" t="s">
+        <v>170</v>
       </c>
       <c r="B41" s="34"/>
       <c r="C41" s="34"/>
       <c r="D41" s="24" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E41" s="4"/>
       <c r="F41" s="31">
@@ -3061,15 +3194,15 @@
       <c r="O41" s="31"/>
     </row>
     <row r="42" spans="1:15">
-      <c r="A42" s="4">
-        <v>29</v>
+      <c r="A42" s="44" t="s">
+        <v>171</v>
       </c>
       <c r="B42" s="34"/>
       <c r="C42" s="34" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D42" s="24" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E42" s="4"/>
       <c r="F42" s="31">
@@ -3086,13 +3219,13 @@
       <c r="O42" s="31"/>
     </row>
     <row r="43" spans="1:15">
-      <c r="A43" s="4">
-        <v>30</v>
+      <c r="A43" s="44" t="s">
+        <v>172</v>
       </c>
       <c r="B43" s="34"/>
       <c r="C43" s="34"/>
       <c r="D43" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E43" s="4"/>
       <c r="F43" s="31">
@@ -3109,13 +3242,13 @@
       <c r="O43" s="31"/>
     </row>
     <row r="44" spans="1:15">
-      <c r="A44" s="4">
-        <v>31</v>
+      <c r="A44" s="44" t="s">
+        <v>173</v>
       </c>
       <c r="B44" s="34"/>
       <c r="C44" s="34"/>
       <c r="D44" s="24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E44" s="4"/>
       <c r="F44" s="31">
@@ -3132,13 +3265,13 @@
       <c r="O44" s="31"/>
     </row>
     <row r="45" spans="1:15">
-      <c r="A45" s="4">
-        <v>32</v>
+      <c r="A45" s="44" t="s">
+        <v>174</v>
       </c>
       <c r="B45" s="34"/>
       <c r="C45" s="34"/>
       <c r="D45" s="15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E45" s="4"/>
       <c r="F45" s="31">
@@ -3154,28 +3287,28 @@
       <c r="N45" s="31"/>
       <c r="O45" s="31"/>
     </row>
+    <row r="46" spans="1:15">
+      <c r="F46" s="2">
+        <v>1</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
     <row r="47" spans="1:15">
-      <c r="A47" s="2">
-        <v>1</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>101</v>
-      </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
+      <c r="F47" s="2">
+        <v>2</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>101</v>
+      </c>
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
     </row>
     <row r="48" spans="1:15">
-      <c r="A48" s="2">
-        <v>2</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>102</v>
-      </c>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
@@ -3186,6 +3319,37 @@
     </row>
   </sheetData>
   <mergeCells count="47">
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="A14:O14"/>
+    <mergeCell ref="F42:O42"/>
+    <mergeCell ref="F43:O43"/>
+    <mergeCell ref="F44:O44"/>
+    <mergeCell ref="F45:O45"/>
+    <mergeCell ref="F36:O36"/>
+    <mergeCell ref="F37:O37"/>
+    <mergeCell ref="F38:O38"/>
+    <mergeCell ref="F39:O39"/>
+    <mergeCell ref="F40:O40"/>
+    <mergeCell ref="F41:O41"/>
+    <mergeCell ref="F26:O26"/>
+    <mergeCell ref="F35:O35"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F16:O16"/>
+    <mergeCell ref="F17:O17"/>
+    <mergeCell ref="F18:O18"/>
+    <mergeCell ref="F19:O19"/>
+    <mergeCell ref="F15:O15"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="F20:O20"/>
+    <mergeCell ref="F31:O31"/>
+    <mergeCell ref="F32:O32"/>
+    <mergeCell ref="F33:O33"/>
+    <mergeCell ref="F34:O34"/>
+    <mergeCell ref="F21:O21"/>
     <mergeCell ref="F22:O22"/>
     <mergeCell ref="F23:O23"/>
     <mergeCell ref="F24:O24"/>
@@ -3202,37 +3366,6 @@
     <mergeCell ref="F29:O29"/>
     <mergeCell ref="F30:O30"/>
     <mergeCell ref="D34:D35"/>
-    <mergeCell ref="F26:O26"/>
-    <mergeCell ref="F35:O35"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F16:O16"/>
-    <mergeCell ref="F17:O17"/>
-    <mergeCell ref="F18:O18"/>
-    <mergeCell ref="F19:O19"/>
-    <mergeCell ref="F15:O15"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="F20:O20"/>
-    <mergeCell ref="F31:O31"/>
-    <mergeCell ref="F32:O32"/>
-    <mergeCell ref="F33:O33"/>
-    <mergeCell ref="F34:O34"/>
-    <mergeCell ref="F21:O21"/>
-    <mergeCell ref="F42:O42"/>
-    <mergeCell ref="F43:O43"/>
-    <mergeCell ref="F44:O44"/>
-    <mergeCell ref="F45:O45"/>
-    <mergeCell ref="F36:O36"/>
-    <mergeCell ref="F37:O37"/>
-    <mergeCell ref="F38:O38"/>
-    <mergeCell ref="F39:O39"/>
-    <mergeCell ref="F40:O40"/>
-    <mergeCell ref="F41:O41"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="A14:O14"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
